--- a/data/검사DB.xlsx
+++ b/data/검사DB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PNUYH\Desktop\skill_bot\knowledge-bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC668E39-950E-4548-B4F1-18C306CAD498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{899CC37B-9ABD-4A6B-B0C3-75FF2A633D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2F87FC1F-8C22-4E51-817B-6500C8322FA3}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
   <si>
     <t>별칭</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -175,20 +175,13 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>부착 후 일상생활 가능</t>
+    <t>검사명</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>제거 시 전원 OFF 후 커프 제거
-검사 종료 후 기기는 심장기능검사실로 전달</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>검사명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>검사후간호</t>
+검사 종료 후 기기는 심장기능검사실로 전달
+부착 후 일상생활 가능</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -265,14 +258,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -588,7 +581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7C04F03-2280-4493-9AE2-2C40B153086F}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.875" customWidth="1"/>
@@ -597,40 +590,36 @@
     <col min="4" max="4" width="16.5" style="1" customWidth="1"/>
     <col min="5" max="5" width="35.125" customWidth="1"/>
     <col min="6" max="6" width="39.5" customWidth="1"/>
-    <col min="7" max="7" width="24.5" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="4" t="s">
+    <row r="1" spans="1:8" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="33" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -646,17 +635,17 @@
       <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I2">
+      <c r="H2">
         <v>1598</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="33" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -672,14 +661,14 @@
       <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I3">
+      <c r="H3">
         <v>1593</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="33" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -695,17 +684,17 @@
       <c r="E4" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="G4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I4">
+      <c r="H4">
         <v>1593</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -721,14 +710,14 @@
       <c r="F5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I5">
+      <c r="H5">
         <v>1598</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="33" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -738,20 +727,23 @@
       <c r="C6" t="s">
         <v>6</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="E6" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="F6" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="G6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I6">
+      <c r="H6">
         <v>1598</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="33" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -767,13 +759,10 @@
       <c r="F7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I7">
+      <c r="H7">
         <v>1598</v>
       </c>
     </row>

--- a/data/검사DB.xlsx
+++ b/data/검사DB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PNUYH\Desktop\skill_bot\knowledge-bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{899CC37B-9ABD-4A6B-B0C3-75FF2A633D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9494F5C-E0B7-4C47-BB84-E3828BDC0D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2F87FC1F-8C22-4E51-817B-6500C8322FA3}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="47">
   <si>
     <t>별칭</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -182,6 +182,65 @@
     <t>제거 시 전원 OFF 후 커프 제거
 검사 종료 후 기기는 심장기능검사실로 전달
 부착 후 일상생활 가능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EPS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전기생리학검사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6 ~ 8시간 NPO (오전 검사시 MN NPO / 오후 검사시 아침식후 NPO)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동의서(EPS: 전기생리학 검사 도자절제술 동의서, 진단명이 A.fib인 경우 심방세동 도자절제술 동의서)
+OP gown 착용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[검사 전]
+항부정맥제는 3 ~ 4일전 투약 중단 – 담당의와 상의
+진단명 A.fib인 경우 Foley cath. Keep
+[검사 후]
+V/S check : 30분 간격으로 2회, EKG check
+Rt. jugular &amp; Femoral. vein : 4시간 이상 sandbag으로 compression후 remove</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중앙진료동 2층 심혈관촬영실</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CBA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>냉각풍선 절제술</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">MNNPO </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lt. arm 20G Fluid keep (3-way 3개 연결)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lt. arm / 20G Fluid keep (3-way 3개 연결)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[검사 전]
+항부정맥제는 3 ~ 4일전 투약 중단 – 담당의와 상의
+xarelto, lixiana, eliquis 등의 약물을 복용 중인 경우 시술 당일 hold
+[검사 후]
+시술 당일 NPO 유지, 익일 아침 sips 후 LD→SD→TD 순으로 식이 시작
+both femoral의 3-way는 시술 당일 유지</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -189,7 +248,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -222,6 +281,13 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -251,7 +317,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -265,6 +331,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -581,12 +650,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7C04F03-2280-4493-9AE2-2C40B153086F}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.875" customWidth="1"/>
     <col min="2" max="2" width="22.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.625" customWidth="1"/>
+    <col min="3" max="3" width="18.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="16.5" style="1" customWidth="1"/>
     <col min="5" max="5" width="35.125" customWidth="1"/>
     <col min="6" max="6" width="39.5" customWidth="1"/>
@@ -600,7 +669,7 @@
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
@@ -626,7 +695,7 @@
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -652,7 +721,7 @@
       <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -675,7 +744,7 @@
       <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -701,7 +770,7 @@
       <c r="B5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -724,7 +793,7 @@
       <c r="B6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -750,7 +819,7 @@
       <c r="B7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -764,6 +833,49 @@
       </c>
       <c r="H7">
         <v>1598</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="132" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="148.5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/data/검사DB.xlsx
+++ b/data/검사DB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PNUYH\Desktop\skill_bot\knowledge-bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9494F5C-E0B7-4C47-BB84-E3828BDC0D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{537BBDFA-9156-4D9C-85D8-828532F228DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2F87FC1F-8C22-4E51-817B-6500C8322FA3}"/>
   </bookViews>

--- a/data/검사DB.xlsx
+++ b/data/검사DB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PNUYH\Desktop\skill_bot\knowledge-bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{537BBDFA-9156-4D9C-85D8-828532F228DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB8673F-FCB0-45C2-B824-A8A94E0767C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2F87FC1F-8C22-4E51-817B-6500C8322FA3}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="52">
   <si>
     <t>별칭</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -199,15 +199,6 @@
   <si>
     <t>동의서(EPS: 전기생리학 검사 도자절제술 동의서, 진단명이 A.fib인 경우 심방세동 도자절제술 동의서)
 OP gown 착용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[검사 전]
-항부정맥제는 3 ~ 4일전 투약 중단 – 담당의와 상의
-진단명 A.fib인 경우 Foley cath. Keep
-[검사 후]
-V/S check : 30분 간격으로 2회, EKG check
-Rt. jugular &amp; Femoral. vein : 4시간 이상 sandbag으로 compression후 remove</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -241,6 +232,53 @@
 [검사 후]
 시술 당일 NPO 유지, 익일 아침 sips 후 LD→SD→TD 순으로 식이 시작
 both femoral의 3-way는 시술 당일 유지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ICD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삽입형 제세동기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[검사 전]
+- Warfarin 복용중인 환자는 48시간 전에 끊고 PT(INR)이 1.5 이하시 시행
+- Heparin 주입중일 경우 6 ~ 8시간 전 infusion stop
+- Shaving (both arm &amp; inguinal)
+- Abx: 시술 전 AST 후 angio실로 보내고 시술 후 Cefa 1g tid
+[검사 후]
+- V/S check : 30분 간격으로 2회
+- EKG &amp; Chest AP x-ray check
+- ICD 삽입한 부위 팔 elevation 금함, 시술 다음 날 chest PA 시행 후 확인까지 ABR
+- ICD site dressing : 검사 다음날부터 일주일간 simple dressing, 일주일후 stich out</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[검사 전]
+- 항부정맥제는 3 ~ 4일전 투약 중단 (담당의와 상의)
+- 진단명 A.fib인 경우 Foley cath. Keep
+[검사 후]
+- V/S check : 30분 간격으로 2회, EKG check
+- Rt. jugular &amp; Femoral. vein : 4시간 이상 sandbag으로 compression후 remove</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[준비]
+- 동의서(심실제세동기 이식 동의서)
+- OP gown 착용
+[검사 전 간호]
+- Warfarin 복용중인 환자는 48시간 전에 끊고 PT(INR)이 1.5 이하시 시행
+- Heparin 주입중일 경우 6 ~ 8시간 전 infusion stop
+- Shaving (both arm &amp; inguinal)
+- Abx: 시술 전 AST 후 angio실로 보내고 시술 후 Cefa 1g tid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[검사 전 간호]
+항부정맥제는 3 ~ 4일전 투약 중단 – 담당의와 상의
+xarelto, lixiana, eliquis 등의 약물을 복용 중인 경우 시술 당일 hold</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -650,7 +688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7C04F03-2280-4493-9AE2-2C40B153086F}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.875" customWidth="1"/>
@@ -835,7 +873,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="132" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -846,36 +884,65 @@
         <v>37</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="H8">
         <v>1458</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="148.5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="165" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="264" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>46</v>
+      <c r="E10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/data/검사DB.xlsx
+++ b/data/검사DB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PNUYH\Desktop\skill_bot\knowledge-bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB8673F-FCB0-45C2-B824-A8A94E0767C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{806ED450-F80E-4F66-A37E-1C5A458BE5AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2F87FC1F-8C22-4E51-817B-6500C8322FA3}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="84">
   <si>
     <t>별칭</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -186,10 +186,6 @@
   </si>
   <si>
     <t>EPS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전기생리학검사</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -281,12 +277,254 @@
 xarelto, lixiana, eliquis 등의 약물을 복용 중인 경우 시술 당일 hold</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>전기생리학검사, R FCA, 전극도자절제술</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEVAR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테바</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[검사 후]
+- lumbar dainage 관리
+- Tragus 10cm, 체위변경이나 이동 시 clamp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TAVI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>양팔 20G keep</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[준비]
+- 동의서(경피적 대동맥 판막 치환술, 예정수혈, 중환자실 입실, 성인진정)
+- 시술복
+- 시술 당일 자정 foley keep
+- 충전된 infusion pump 3개, 성인진정기록지 동반</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[검사 전]
+- 동의서(경피적 대동맥 판막 치환술, 예정수혈, 중환자실 입실, 성인진정)
+- 시술복
+- 시술 당일 자정 foley keep
+- 충전된 infusion pump 3개, 성인진정기록지 동반
+[검사 후]
+- 시술 후 1day ICU monitoring
+- 시술 중 TPM 삽입 진행함. 병동 전동 후에도 EKG monitoring 유지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흉부외과 기본 수술</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>32병동 TS, 32w TS, TS OP, TS수술, TS 수술</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20G keep</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[준비]
+- 검사: Ab+cross matching &amp; 수혈신청
+- 사지 BP, CHG 샤워
+- 동의서(수술, 수혈, ICU)
+- 리노로신: 전날 저녁, 당일 OP전 점적
+[수술 당일]
+- 체중측정
+- Gaster, Ambroxol IV
+- Cefazoline AST확인 후 OR 전송</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[준비]
+- 검사: Ab+cross matching &amp; 수혈신청
+- 사지 BP, CHG 샤워
+- 동의서(수술, 수혈, ICU)
+- 리노로신: 전날 저녁, 당일 OP전 점적
+[수술 당일]
+- 체중측정
+- Gaster, Ambroxol IV
+- Cefazoline AST확인 후 OR 전송
+[수술 후]
+OP site, CT, JP, EKG 확인
+Cefazoline 익일 D/C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nephrectomy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>술 전 날 저녁 SD, MN NPO 교육
+* 자기 전 glycerin enema</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[준비물]
+- 복대 수가코드 EZ RAP ABDO BACK BRACE
+- IPC cuff 수가코드 FLOWTRON EXCEL GARMENT(THIGH) 
+- laparoscopic인 경우 비뇨의학과용 복강경 필터를 1층 의료용품점에서 구입
+[수술 전]
+- abdomen shaving
+- 고혈압약 및 갑상선약(synthyroid)은 수술 당일 아침 물 소량과 함께 복용하도록 교육하기
+- antibody screening &amp; cross matching 검사 및 수혈 동의서 필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>네프렉토미, 신절제술, Adrenalectomy, 부신절제술</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중앙진료동 2층 수술실</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>* Nephrectomy와 Adrenalectomy는 준비물과 술전후 간호가 같습니다.
+[수술 전]
+- abdomen shaving
+- 고혈압약 및 갑상선약(synthyroid)은 수술 당일 아침 물 소량과 함께 복용하도록 교육하기
+- antibody screening &amp; cross matching 검사 및 수혈 동의서 필요
+[수술 후]
+- gas out 후 NPO 해제(SOW부터 진행)
+- POD#3 PCA, foley 제거, self voiding 후 PVR시행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thyroidectomy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>갑상선절제술</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20G + 3way line keep</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[준비물]
+- DIS#2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[수술 후]
+- 의식 alert, 수술 후 6시간 뒤 SOW 가능
+- 목이 붓거나 숨이 찬 증상 확인(응급)
+- 저린 증상 있을 시: Ca lab후 IV
+- 동위원소 날짜 잡히면 해당과 처방에 따라 식이 진행
+- S/O 안함(녹는 실)
+- 퇴원 협진: Total-핵의학과, 내분비 / Subtotal-내분비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LMS with lasering</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tonsilectomy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adenoidectomy, 톤실렉토미, 아데노이덱토미, 편도절제술</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>술전 베타딘 가글</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">* tonsilectomy와 Adrenoidectomy는 준비물과 술전후 간호가 같습니다.
+[수술 전]
+베타딘 가글
+[수술 후]
+- 술 후 얼음 팩
+- 출혈 있을 시 삼키지 말 것 교육
+- 찬 음식 1주일 섭취
+- NPO release 후 부터 Gargling 격려 하루 8회 이상, 많이 역겨울시 물과 1:1로 희석하여 사용
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>▪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 1% betadine Gargling : 수술부위 소독효과 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>▪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tantum gargling, Tantum verde(spray) : 수술 부위 통증 완화</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[준비물]
+- laser tube(이비인후과용) - 의료용품점에서 환자가 구입, 사용하지 않은 경우 환불 할 수 있으므로 케이스 제거 등 훼손 금지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LMS, LMS /c lasering, LMS /c, 코맨도, 코만도, COMMANDO, COMANDO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>* COMMANDO와 LMS /c lasering은 준비물과 술전후 간호가 같습니다.
+[수술 후]
+- 절대 음성 안정
+- 하루에 최소한 2L 이상의 물을 섭취하도록 한다.
+- 퇴원 후 이비인후과 외래에서 laser tube 찾아가도록 안내</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -325,6 +563,12 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -688,7 +932,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7C04F03-2280-4493-9AE2-2C40B153086F}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.875" customWidth="1"/>
@@ -878,22 +1122,22 @@
         <v>35</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="H8">
         <v>1458</v>
@@ -901,25 +1145,25 @@
     </row>
     <row r="9" spans="1:8" ht="165" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="D9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="G9" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H9">
         <v>1458</v>
@@ -927,23 +1171,191 @@
     </row>
     <row r="10" spans="1:8" ht="264" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="G10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="198" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="231" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="247.5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="148.5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="148.5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="280.5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" t="s">
+        <v>79</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/검사DB.xlsx
+++ b/data/검사DB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PNUYH\Desktop\skill_bot\knowledge-bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{806ED450-F80E-4F66-A37E-1C5A458BE5AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C595D81-D73E-4F1F-8DD0-6FDC4FA33DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2F87FC1F-8C22-4E51-817B-6500C8322FA3}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="97">
   <si>
     <t>별칭</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -411,6 +411,9 @@
   <si>
     <t>갑상선절제술</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20G + 3way line keep</t>
   </si>
   <si>
     <t>20G + 3way line keep</t>
@@ -517,6 +520,64 @@
 - 절대 음성 안정
 - 하루에 최소한 2L 이상의 물을 섭취하도록 한다.
 - 퇴원 후 이비인후과 외래에서 laser tube 찾아가도록 안내</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Parotidectomy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>키미테 이틀마다 교환</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(-)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">파로티덱토미, 이하선 절제술 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mastoidectomy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tympanoplasty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수술 후 6시간 금식
+수술 부위 2일정도 압박상태 유지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ESS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부비동 내시경 수술, Endoscopic sinus surgery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MNNPO</t>
+  </si>
+  <si>
+    <t>코털 제거
+수술 후 코세척 준비물
+- 노즈비데: 1층 의료기상사
+- 생리식염수: 약국</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[수술 전]
+코털 제거
+[수술 후]
+수술 후 6시간 금식
+수술 후 1일부터 퇴원 당일까지 매일 아침 41병동 이비인후과 치료실에서 드레싱
+- 문수진 교수님: 수술 2일째 지혈 드레싱 제제 제거
+- 박지환 교수님: 제거 하지 않고 퇴원
+- 퇴원 전 코 세척, 코 스프레이 사용 교육(Dx 제거 또는 녹은 뒤 2일 후)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -932,7 +993,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7C04F03-2280-4493-9AE2-2C40B153086F}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.875" customWidth="1"/>
@@ -1278,7 +1339,7 @@
         <v>66</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>67</v>
@@ -1301,13 +1362,13 @@
         <v>41</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>69</v>
@@ -1315,47 +1376,103 @@
     </row>
     <row r="16" spans="1:8" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="280.5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="198" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E17" t="s">
-        <v>79</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
+      <c r="E20" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>96</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/검사DB.xlsx
+++ b/data/검사DB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PNUYH\Desktop\skill_bot\knowledge-bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C595D81-D73E-4F1F-8DD0-6FDC4FA33DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB160DE-8B05-433D-A657-619FEA822D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2F87FC1F-8C22-4E51-817B-6500C8322FA3}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="105">
   <si>
     <t>별칭</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -448,6 +448,110 @@
   </si>
   <si>
     <t>술전 베타딘 가글</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[준비물]
+- laser tube(이비인후과용) - 의료용품점에서 환자가 구입, 사용하지 않은 경우 환불 할 수 있으므로 케이스 제거 등 훼손 금지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LMS, LMS /c lasering, LMS /c, 코맨도, 코만도, COMMANDO, COMANDO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>* COMMANDO와 LMS /c lasering은 준비물과 술전후 간호가 같습니다.
+[수술 후]
+- 절대 음성 안정
+- 하루에 최소한 2L 이상의 물을 섭취하도록 한다.
+- 퇴원 후 이비인후과 외래에서 laser tube 찾아가도록 안내</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Parotidectomy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>키미테 이틀마다 교환</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(-)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">파로티덱토미, 이하선 절제술 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mastoidectomy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tympanoplasty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수술 후 6시간 금식
+수술 부위 2일정도 압박상태 유지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ESS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부비동 내시경 수술, Endoscopic sinus surgery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MNNPO</t>
+  </si>
+  <si>
+    <t>코털 제거
+수술 후 코세척 준비물
+- 노즈비데: 1층 의료기상사
+- 생리식염수: 약국</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[수술 전]
+코털 제거
+[수술 후]
+수술 후 6시간 금식
+수술 후 1일부터 퇴원 당일까지 매일 아침 41병동 이비인후과 치료실에서 드레싱
+- 문수진 교수님: 수술 2일째 지혈 드레싱 제제 제거
+- 박지환 교수님: 제거 하지 않고 퇴원
+- 퇴원 전 코 세척, 코 스프레이 사용 교육(Dx 제거 또는 녹은 뒤 2일 후)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고용량 스테로이드 치료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고용량 스테로이드 사용 동의서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제한 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carbogen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카보겐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(1) 입원당일부터 매일 30분간 하루2회 시행
+(2) 수가 : 산소흡입(1일당) 수량 1, 혼합가스(O2:95%+CO2:5%)-안과(LOCAL) 수량 2 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고용량스테로이드치료, 스테로이드치료, 스테로이드펄스, 펄스치료, 펄스, Steroid pulse. Pulse therapy, Hearing loss, 청력손상, 안면마비, Facial palsy</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -464,7 +568,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="9"/>
         <color theme="1"/>
         <rFont val="Segoe UI Symbol"/>
         <family val="2"/>
@@ -473,7 +577,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="9"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
         <family val="2"/>
@@ -485,7 +589,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="9"/>
         <color theme="1"/>
         <rFont val="Segoe UI Symbol"/>
         <family val="2"/>
@@ -494,7 +598,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="9"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
         <family val="2"/>
@@ -506,78 +610,25 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[준비물]
-- laser tube(이비인후과용) - 의료용품점에서 환자가 구입, 사용하지 않은 경우 환불 할 수 있으므로 케이스 제거 등 훼손 금지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LMS, LMS /c lasering, LMS /c, 코맨도, 코만도, COMMANDO, COMANDO</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>* COMMANDO와 LMS /c lasering은 준비물과 술전후 간호가 같습니다.
-[수술 후]
-- 절대 음성 안정
-- 하루에 최소한 2L 이상의 물을 섭취하도록 한다.
-- 퇴원 후 이비인후과 외래에서 laser tube 찾아가도록 안내</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Parotidectomy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>키미테 이틀마다 교환</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(-)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">파로티덱토미, 이하선 절제술 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mastoidectomy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tympanoplasty</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수술 후 6시간 금식
-수술 부위 2일정도 압박상태 유지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ESS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>부비동 내시경 수술, Endoscopic sinus surgery</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MNNPO</t>
-  </si>
-  <si>
-    <t>코털 제거
-수술 후 코세척 준비물
-- 노즈비데: 1층 의료기상사
-- 생리식염수: 약국</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[수술 전]
-코털 제거
-[수술 후]
-수술 후 6시간 금식
-수술 후 1일부터 퇴원 당일까지 매일 아침 41병동 이비인후과 치료실에서 드레싱
-- 문수진 교수님: 수술 2일째 지혈 드레싱 제제 제거
-- 박지환 교수님: 제거 하지 않고 퇴원
-- 퇴원 전 코 세척, 코 스프레이 사용 교육(Dx 제거 또는 녹은 뒤 2일 후)</t>
+    <t>** Hearing loss
+[경구]
+methylon(methylprednisolon) 4mg 12tab 10일간 투여 후 8tab, 6tab, 4tab, 2tab 감량함.
+[수액]
+혈액순환 개선제, 혈장량 증가제, 비타민등 수액 주입
+보통 N/S 500ml+M.V.H 1vial 20cc/hr, N/S 500ml+TANAMIN 2amp 20cc/hr 함께사용
+[보조치료]
+carbogen Tx, ITI
+** Facial Palsy
+[수액]
+(1) N/S 150ml+cortisolu(Hydrocortisone) mix 하여 1시간 동안 주입(입원 당일 처방남 시간에 익일부터 7Am 시작)
+(2) cortisolu 용량은 500mg으로 start하여 500mg→300mg→300mg→200mg→200mg→100mg→100mg 으로 용량 줄여가며 일주일간 사용
+(2) 에크로바(aclova) 항바이러스제는 N/S 100ml(bottle)에 mix하여 1시간 동안 주입, BID 용법, 5일동안 사용
+[경구]
+비타민제, 제산제, 소염진통제 등 사용
+[안약, 안연고]
+(HYALEIN-수시로, TARIVID-HS) : palsy 있는 쪽 눈에 사용
+[보조치료]
+carbogen, 재활의학과 안면 열전기치료 QD</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -585,7 +636,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -611,7 +662,7 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -619,14 +670,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Segoe UI Symbol"/>
       <family val="2"/>
@@ -660,12 +719,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -673,10 +735,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -993,7 +1058,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7C04F03-2280-4493-9AE2-2C40B153086F}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.875" customWidth="1"/>
@@ -1005,474 +1070,529 @@
     <col min="7" max="7" width="16.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:8" s="2" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="33" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:8" ht="24" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="5">
         <v>1598</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="33" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:8" ht="24" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="F3" s="5"/>
+      <c r="G3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="5">
         <v>1593</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="33" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="4" spans="1:8" ht="24" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="5">
         <v>1593</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="5" spans="1:8" ht="24" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="E5" s="5"/>
+      <c r="F5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="5">
         <v>1598</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="33" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:8" ht="24" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="5">
         <v>1598</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="7" spans="1:8" ht="36" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="E7" s="5"/>
+      <c r="F7" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="5">
         <v>1598</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="148.5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="8" spans="1:8" ht="96" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="5">
         <v>1458</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="165" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="9" spans="1:8" ht="108" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="5">
         <v>1458</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="264" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="10" spans="1:8" ht="180" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="5">
         <v>1458</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="11" spans="1:8" ht="36" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="E11" s="5"/>
+      <c r="F11" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="5">
         <v>1458</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="198" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="12" spans="1:8" ht="132" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="5">
         <v>1458</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="231" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="13" spans="1:8" ht="168" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="6" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="247.5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="H13" s="5"/>
+    </row>
+    <row r="14" spans="1:8" ht="156" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" s="6" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" ht="148.5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" spans="1:8" ht="84" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" s="6" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" ht="148.5" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" spans="1:8" ht="96" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="G16" s="6"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" ht="192" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D17" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F16" s="1" t="s">
+      <c r="E17" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G17" s="6"/>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="280.5" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>78</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="B18" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D18" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E17" t="s">
-        <v>80</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="33" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="E18" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F18" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="G18" s="6"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" ht="24" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C19" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D19" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F18" s="1" t="s">
+      <c r="E19" s="6" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="33" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="F19" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F19" s="1" t="s">
+      <c r="G19" s="6"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" ht="132" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="198" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="B20" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E20" s="1" t="s">
+      <c r="F20" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="G20" s="6"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
         <v>96</v>
       </c>
+      <c r="B21" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G21" s="6"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" ht="36" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="G22" s="6"/>
+      <c r="H22" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/검사DB.xlsx
+++ b/data/검사DB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PNUYH\Desktop\skill_bot\knowledge-bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB160DE-8B05-433D-A657-619FEA822D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE25B08-E2BD-4630-B602-77636760C031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2F87FC1F-8C22-4E51-817B-6500C8322FA3}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="113">
   <si>
     <t>별칭</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -631,12 +631,778 @@
 carbogen, 재활의학과 안면 열전기치료 QD</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>TLH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TBSO, LOC, D&amp;C, Hysterectomy, 히스테렉토미, 복강경 자궁절제술, 자궁절제술, 난소절제술. OBGY OP, OBGY 수술</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전날 6pm NPO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[송용중, 김휘곤 교수님 공통사항]
+- 전날 7PM, 9PM 글리세린 enema
+- 당일 6am dulcolax 2Ea
+- (처방에 따라) Gastotec(misoprostol) 1T 복용 혹은 질내 삽입 (김:질내 /송,하:PO)
+- All (회음부 전체~항문) Shaving (virgin일 경우 Bikini line)
+- 20G keep, 김휘곤 5%DW nak2 150cc/hr 송용중/하형인 100cc/hr
+*신부전, 심장질환 병력있는 경우 확인후 수액속도 조절필요
+- BSO, LOC 등의 경우 수술부위 표지 필요
+- 송, 하 교수님은 D&amp;C 제외 모든환자에게 혈전예방스타킹 사용(신고 OR방
+[준비물]
+- 복강경 필터 수술 시 사용 안 할 수 있어 구입 시 영수증 챙기도록 설명하기
+* Pf. 김휘곤 / PA 김혜선: 복대, 복강경 필터(N-tox filter), 제모크림
+* Pf. 송용중 / PA 문가영: 복대, 복강경 필터(core smofil), 제모크림, inspirometer, antiembolism stocking(2개), 중증 or explolapa 시 penko 챙기기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">[주의사항]
+* pre OP 검체바코드 OR에 안 내림
+* 질정제 6pm으로 처방나도 10pm에 투여, 약이 흐를 수 있어 넣고 나면 누워있기 생리통처럼 통증 또는 약간의 출혈 동반될 수 있음 
+진통제 요청 시 PRN ketocin or Denogan 투여
+[수술 후]
+*김휘곤 교수님
+- 술 당일 U/O q4hr(50cc미만 노티)
+- Foley POD#1 6am remove, self voiding 1회 확인
+-(colpopexy: 1회 training 후 제거)
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCD 사이즈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>📏</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Stocking </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>및</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Immobilizer </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>측정법</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>둘레</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>측정값</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + 5cm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>기준으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> size </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>측정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>양쪽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>둘레</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>측정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>후</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>큰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>사이즈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>기준으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>수가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>종아리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> calf]
+S : 29~35
+M : 34~40
+L : 39~45
+XL : 44~51
+[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>넓적다리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> thigh]
+S : 43~54
+M : 48~60
+L : 54~66
+XL : 60~72
+[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>제품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">]
+S/M/L : TED Anti embolism stocking
+XL : Thrombo X stocking Long
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>※</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>스타킹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, SCD </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>각</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>수기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>※</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>환자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>적용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>여분</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>지급</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>※</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>오염</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>교체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>교육</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스타킹사이즈,
+스타킹 사이즈,
+스타킹측정,
+스타킹 측정,
+SCD사이즈,
+압박스타킹,
+TED스타킹,
+stocking</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -649,14 +1415,6 @@
       <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -690,6 +1448,20 @@
       <name val="Segoe UI Symbol"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -719,29 +1491,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1058,541 +1827,558 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7C04F03-2280-4493-9AE2-2C40B153086F}">
-  <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.875" customWidth="1"/>
-    <col min="2" max="2" width="22.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="35.125" customWidth="1"/>
-    <col min="6" max="6" width="39.5" customWidth="1"/>
-    <col min="7" max="7" width="16.25" style="1" customWidth="1"/>
+    <col min="1" max="1" width="45.875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="22.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5" style="4" customWidth="1"/>
+    <col min="4" max="4" width="16.5" style="4" customWidth="1"/>
+    <col min="5" max="5" width="35.125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="39.5" style="3" customWidth="1"/>
+    <col min="7" max="7" width="16.25" style="4" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="24" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="3">
         <v>1598</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="3">
         <v>1593</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="24" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="3">
         <v>1593</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="24" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="3">
         <v>1598</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="24" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="3">
         <v>1598</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="36" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="3">
         <v>1598</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="96" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="3">
         <v>1458</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="108" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="3">
         <v>1458</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="180" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="3">
         <v>1458</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="36" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="3">
         <v>1458</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="132" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="3">
         <v>1458</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="168" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="H13" s="5"/>
     </row>
     <row r="14" spans="1:8" ht="156" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:8" ht="84" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:8" ht="96" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="G16" s="6"/>
-      <c r="H16" s="5"/>
     </row>
-    <row r="17" spans="1:8" ht="192" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:6" ht="192" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="G17" s="6"/>
-      <c r="H17" s="5"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="G18" s="6"/>
-      <c r="H18" s="5"/>
     </row>
-    <row r="19" spans="1:8" ht="24" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="1:6" ht="24" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="G19" s="6"/>
-      <c r="H19" s="5"/>
     </row>
-    <row r="20" spans="1:8" ht="132" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="G20" s="6"/>
-      <c r="H20" s="5"/>
     </row>
-    <row r="21" spans="1:8" ht="409.5" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="1:6" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="G21" s="6"/>
-      <c r="H21" s="5"/>
     </row>
-    <row r="22" spans="1:8" ht="36" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="1:6" ht="36" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="6" t="s">
+      <c r="C22" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="G22" s="6"/>
-      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="1:6" ht="372" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="288" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>111</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/검사DB.xlsx
+++ b/data/검사DB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PNUYH\Desktop\skill_bot\knowledge-bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE25B08-E2BD-4630-B602-77636760C031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78B9A49-66FA-4D24-AC29-C74B1484EA06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2F87FC1F-8C22-4E51-817B-6500C8322FA3}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="125">
   <si>
     <t>별칭</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1397,12 +1397,113 @@
 stocking</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>참고URL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기침유발기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코프머신, MI-E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/pnuyhieum/356</t>
+  </si>
+  <si>
+    <t>① 환자 상태에 맞는 회로(마스크/기도연결관) 준비
+② 전원 ON → 압력 0 확인
+③ 환자 회로를 막은 상태에서
+- 호기압(음압) 설정
+- 흡기압(양압) 설정
+※ 흡기압은 호기압의 50~100% 범위
+※ 기흉 위험 시 흡기압 낮게 설정
+④ 흡기·호기 압력이 정상 작동하는지 확인
+⑤ 환자 체위
+- 앙와위/측와위: 침상 15~45°
+- 좌위: 상체 60~90°
+⑥ 낮은 압력부터 시작하여 단계적으로 증가
+⑦ "들이쉬고-내쉬고"에 맞춰 기침 유도
+⑧ 분비물 배출 시
+- 마스크 제거 또는 흡인 시행
+⑨ 5회 시행 후
+- 과환기 예방 위해 20~30초 휴식
+⑩ 치료 중 모니터링
+- 산소포화도
+- 기도 확보 상태
+- 환자 피로도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/pnuyhieum/96</t>
+  </si>
+  <si>
+    <t>히크만카테터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hickman
+히크만
+히크만카테터
+히크만 삽입
+히크만 제거</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[삽입]
+① 영상의학과 타과의뢰
+② 동의서 준비
+③ 시술복 착용
+④ Peripheral IV keep
+⑤ 침습적 시술 전 환자상태 확인표 작성
+[제거]
+① 영상의학과 타과의뢰(회신확인)
+② 제거 동의서 준비
+③ 시술복 착용
+④ Peripheral IV keep
+⑤ 침습적 시술 전 환자상태 확인표 작성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[적응증]
+- 조혈모세포이식
+- 항암제/항생제 투여
+- 총비경구영양(TPN)
+- 잦은 채혈
+[시술 후]
+① 흉부 X-ray 확인
+② 활력징후 측정
+③ 출혈 여부 확인
+④ 통증 사정
+⑤ 도관 patency 확인
+⑥ 간호일지 및 케어플랜 작성
+[카테터 관리]
+- 수혈/채혈 후 NS 10ml 이상 flushing
+- 3ml 이하 주사기 사용 금지
+- 캡 개방 전 클램프 잠금 확인
+- patency 매일 확인
+- Heparin locking 주 1회
+[Flushing &amp; Locking]
+- NS 10ml
+- Heparin 500unit/5ml</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>혈관조영실</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/pnuyhieum/200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1462,6 +1563,15 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1486,12 +1596,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1513,9 +1626,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1827,20 +1947,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7C04F03-2280-4493-9AE2-2C40B153086F}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="19.25" style="3" customWidth="1"/>
     <col min="2" max="2" width="22.25" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.5" style="4" customWidth="1"/>
     <col min="4" max="4" width="16.5" style="4" customWidth="1"/>
-    <col min="5" max="5" width="35.125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="39.5" style="3" customWidth="1"/>
+    <col min="5" max="6" width="57.875" style="3" customWidth="1"/>
     <col min="7" max="7" width="16.25" style="4" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="3"/>
+    <col min="8" max="8" width="9" style="3"/>
+    <col min="9" max="9" width="22.875" style="4" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
@@ -1865,8 +1986,11 @@
       <c r="H1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="I1" s="7" t="s">
+        <v>113</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" ht="24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="24" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -1892,7 +2016,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="24" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
@@ -1915,7 +2039,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="24" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
@@ -1941,7 +2065,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="24" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>22</v>
       </c>
@@ -1964,7 +2088,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="24" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>27</v>
       </c>
@@ -1990,7 +2114,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="36" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>31</v>
       </c>
@@ -2013,7 +2137,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="96" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="96" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>35</v>
       </c>
@@ -2039,7 +2163,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="108" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="108" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
@@ -2065,7 +2189,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="180" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="180" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>45</v>
       </c>
@@ -2091,7 +2215,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="36" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>52</v>
       </c>
@@ -2114,7 +2238,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="132" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="132" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>55</v>
       </c>
@@ -2140,7 +2264,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="168" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="168" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>60</v>
       </c>
@@ -2163,7 +2287,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="156" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="156" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>65</v>
       </c>
@@ -2186,7 +2310,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="84" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="84" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>71</v>
       </c>
@@ -2209,7 +2333,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="96" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="96" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>77</v>
       </c>
@@ -2229,7 +2353,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="192" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="192" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>78</v>
       </c>
@@ -2249,7 +2373,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>84</v>
       </c>
@@ -2269,7 +2393,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="24" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="24" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>89</v>
       </c>
@@ -2289,7 +2413,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="132" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>91</v>
       </c>
@@ -2309,7 +2433,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>96</v>
       </c>
@@ -2329,7 +2453,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="36" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="36" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>99</v>
       </c>
@@ -2349,7 +2473,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="372" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="372" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>105</v>
       </c>
@@ -2369,7 +2493,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="288" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>110</v>
       </c>
@@ -2378,11 +2502,57 @@
       </c>
       <c r="E24" s="4" t="s">
         <v>111</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="360" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="288" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H26" s="3">
+        <v>1805</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="I26" r:id="rId1" xr:uid="{68B13EAD-92E8-4EE7-B89B-CDCD30067DDC}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/data/검사DB.xlsx
+++ b/data/검사DB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PNUYH\Desktop\skill_bot\knowledge-bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78B9A49-66FA-4D24-AC29-C74B1484EA06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B44A9FF0-835A-4BB3-9A55-06C5350FF660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2F87FC1F-8C22-4E51-817B-6500C8322FA3}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="139">
   <si>
     <t>별칭</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -633,43 +633,6 @@
   </si>
   <si>
     <t>TLH</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TBSO, LOC, D&amp;C, Hysterectomy, 히스테렉토미, 복강경 자궁절제술, 자궁절제술, 난소절제술. OBGY OP, OBGY 수술</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전날 6pm NPO</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[송용중, 김휘곤 교수님 공통사항]
-- 전날 7PM, 9PM 글리세린 enema
-- 당일 6am dulcolax 2Ea
-- (처방에 따라) Gastotec(misoprostol) 1T 복용 혹은 질내 삽입 (김:질내 /송,하:PO)
-- All (회음부 전체~항문) Shaving (virgin일 경우 Bikini line)
-- 20G keep, 김휘곤 5%DW nak2 150cc/hr 송용중/하형인 100cc/hr
-*신부전, 심장질환 병력있는 경우 확인후 수액속도 조절필요
-- BSO, LOC 등의 경우 수술부위 표지 필요
-- 송, 하 교수님은 D&amp;C 제외 모든환자에게 혈전예방스타킹 사용(신고 OR방
-[준비물]
-- 복강경 필터 수술 시 사용 안 할 수 있어 구입 시 영수증 챙기도록 설명하기
-* Pf. 김휘곤 / PA 김혜선: 복대, 복강경 필터(N-tox filter), 제모크림
-* Pf. 송용중 / PA 문가영: 복대, 복강경 필터(core smofil), 제모크림, inspirometer, antiembolism stocking(2개), 중증 or explolapa 시 penko 챙기기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">[주의사항]
-* pre OP 검체바코드 OR에 안 내림
-* 질정제 6pm으로 처방나도 10pm에 투여, 약이 흐를 수 있어 넣고 나면 누워있기 생리통처럼 통증 또는 약간의 출혈 동반될 수 있음 
-진통제 요청 시 PRN ketocin or Denogan 투여
-[수술 후]
-*김휘곤 교수님
-- 술 당일 U/O q4hr(50cc미만 노티)
-- Foley POD#1 6am remove, self voiding 1회 확인
--(colpopexy: 1회 training 후 제거)
-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1496,6 +1459,188 @@
   </si>
   <si>
     <t>https://cafe.naver.com/pnuyhieum/200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TBSO, LOC, D&amp;C, Hysterectomy, 히스테렉토미, 복강경 자궁절제술, 자궁절제술, 난소절제술. OBGY OP, OBGY 수술 TLH
+복강경자궁절제술
+BSO
+난관난소절제술
+LOC
+난소종양제거술
+D&amp;C
+자궁소파술
+부인과수술
+산부인과수술</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수술 전날 18:00 NPO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20G keep
+Pf. 김휘곤
+- 5%DW NaK2 150cc/hr
+Pf. 송용중/하형인
+- 5%DW NaK2 100cc/hr
+※ 신부전/심질환 병력 시 수액속도 확인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 전날 19시, 21시 글리세린 관장
+② 수술 당일 06시 Dulcolax 2정
+③ Gastotec
+- 김휘곤: 질내 삽입
+- 송용중/하형인: PO
+④ All shaving
+(virgin 환자: bikini line)
+⑤ BSO, LOC 수술부위 표지
+⑥ 송용중/하형인
+- D&amp;C 제외 전 환자 antiembolism stocking 착용
+[준비물]
+김휘곤
+- 복대
+- N-tox filter
+- 제모크림
+송용중
+- 복대
+- Core smofil filter
+- 제모크림
+- Inspirometer
+- Antiembolism stocking 2개
+※ 중증/Explolapa 시 Penko 준비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[수술 전]
+- Pre-op 검체 바코드 OR 미전송
+- 질정제는 22시 투여
+- 투여 후 누워있기
+- 생리통 양상 통증 및 소량 출혈 가능
+- 통증 시 PRN Ketocin 또는 Denogan
+[수술 후 공통]
+- G/O 후 식이 진행
+(Sips → CLD → SD → TD)
+- POD#1 ambulation 가능
+- Ambulation 잘하면 stocking 제거
+- Foley 제거 후 POD#1 BWT 1회
+(개복수술은 daily)
+- JP drain
+  · 06시만 count
+  · Milking 금지
+[김휘곤]
+- U/O q4hr
+- Foley POD#1 06시 제거
+- Self voiding 1회 확인
+- Colpopexy는 training 후 제거
+- 외래 7~10일 예약
+[송용중]
+- I/O q4hr
+- Foley POD#1 06시 제거
+- Self voiding 2회 확인
+- 외래 2주 후 예약</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AST 하는 항암제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항암제AST, 항암제 AST
+Skin Test
+Leunase
+Bleocin
+Erbitux
+Cetuximab
+Bleomycin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[LEUNASE]
+- 최초 투여 시 AST 시행
+- 휴약기간이 길어진 경우 AST 시행
+- AST 후 1시간 관찰
+- 발적, 팽윤, 오한, 발열 없으면 투약 가능
+- 7일 이내 재투약 시 AST 불필요
+[BLEOCIN]
+- Test dose 1~2mg IV
+- 1~2시간 관찰 후 본 투약
+[ERBITUX]
+- Test dose(Cetuximab 20mg) 천천히 IV
+- 1시간 관찰 후 본 투약</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>병동 또는 항암치료실</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>루트 필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/pnuyhieum/245</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[LEUNASE]
+- 과민반응 발생률 10~40%
+- 발적, 팽윤, 오한, 발열 관찰
+[BLEOCIN]
+- 림프종 환자 약 1% 과민반응
+- 저혈압, 발열, 의식혼미 주의
+[ERBITUX]
+- 투약 중 과민반응 여부 관찰
+- Test dose(20mg slowly IV)후 1시간 close observation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대장수술 Tattooing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tattooing
+대장 Tattooing
+수술전 Tattooing
+내시경 Tattooing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[입원일(수술 2일 전)]
+① 입원 즉시 NPO
+② 소화기내과 Consult
+- Tattooing 내시경 예약 확인
+③ 장정결
+- Colyte 2L : 입원일 20시~22시 복용
+- Bisacodyl 2T : 22시 복용
+④ 수액 유지
+- 처방에 따라 Total fluid 유지
+⑤ 검사
+- Antibody screening
+- Cross matching
+- BioBank 채혈
+⑥ BioBank 조직 바코드 및 인체유래물 동의서 준비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 내시경 당일 06시 Colyte 2L 추가 복용
+② 손경모 교수 환자
+- Normix 200mg 2T
+- 09시, 18시 복용
+③ Tattooing 후 Abdomen Erect/Supine 촬영
+④ BioBank 바코드 및 인체유래물 동의서는
+수술 당일 OR로 보냄
+⑤ Colyte 복용 중
+오심, 구토, 복부불편감 발생 시 중단 후 Notify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입원 즉시 NPO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://cafe.naver.com/pnuyhieum/153</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1947,12 +2092,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7C04F03-2280-4493-9AE2-2C40B153086F}">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.25" style="3" customWidth="1"/>
-    <col min="2" max="2" width="22.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5" style="4" customWidth="1"/>
+    <col min="2" max="2" width="16.375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="13.25" style="4" customWidth="1"/>
     <col min="4" max="4" width="16.5" style="4" customWidth="1"/>
     <col min="5" max="6" width="57.875" style="3" customWidth="1"/>
     <col min="7" max="7" width="16.25" style="4" customWidth="1"/>
@@ -1987,7 +2132,7 @@
         <v>13</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="24" x14ac:dyDescent="0.3">
@@ -2473,86 +2618,134 @@
         <v>101</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="372" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>105</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="360" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H26" s="3">
         <v>1805</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>124</v>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="204" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="240" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I26" r:id="rId1" xr:uid="{68B13EAD-92E8-4EE7-B89B-CDCD30067DDC}"/>
+    <hyperlink ref="I27" r:id="rId2" xr:uid="{6C77CCE9-EB01-4526-9C4B-1F5BB463D555}"/>
+    <hyperlink ref="I28" r:id="rId3" xr:uid="{7A66397E-6CDC-4ECD-B430-19E93FB05311}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
--- a/data/검사DB.xlsx
+++ b/data/검사DB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PNUYH\Desktop\skill_bot\knowledge-bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B44A9FF0-835A-4BB3-9A55-06C5350FF660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6AC1DEE-F9C3-45ED-8618-AA938C7E2264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2F87FC1F-8C22-4E51-817B-6500C8322FA3}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="145">
   <si>
     <t>별칭</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1547,16 +1547,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>항암제AST, 항암제 AST
-Skin Test
-Leunase
-Bleocin
-Erbitux
-Cetuximab
-Bleomycin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[LEUNASE]
 - 최초 투여 시 AST 시행
 - 휴약기간이 길어진 경우 AST 시행
@@ -1597,13 +1587,6 @@
   </si>
   <si>
     <t>대장수술 Tattooing</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tattooing
-대장 Tattooing
-수술전 Tattooing
-내시경 Tattooing</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1641,6 +1624,62 @@
   </si>
   <si>
     <t>https://cafe.naver.com/pnuyhieum/153</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMA 진단지원사업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 검사 대상 확인
+- 환자만 시행하는지
+- 보호자(부모) 검사 포함인지 확인
+② 검사 시행자 전원 동의서 작성
+③ 제출서류
+- 유전자 검사 동의서
+- 인체유래물 연구 동의서
+④ 주민등록등본 제출
+(주민번호 뒷자리 포함)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 검사 전 희귀질환센터 연락 필수
+② 검사 대상자 모두 동의서 필요
+③ 검사 관련 문의는 이예은 선생님</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>편의시설동 3층 희귀질환센터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3724
+(이예은 선생님)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMA,
+비수도권 진단지원사업,
+SMA 검사,
+SMA 지원사업,
+희귀질환센터 SMA,</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tattooing,
+대장 Tattooing,
+수술전 Tattooing,
+내시경 Tattooing,</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항암제AST, 항암제 AST
+Skin Test,
+Leunase,
+Bleocin,
+Erbitux,
+Cetuximab,
+Bleomycin,</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2092,7 +2131,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7C04F03-2280-4493-9AE2-2C40B153086F}">
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.25" style="3" customWidth="1"/>
@@ -2697,45 +2736,65 @@
         <v>126</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D27" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="I27" s="8" t="s">
         <v>130</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="240" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="F28" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="I28" s="8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="144" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="I28" s="8" t="s">
+      <c r="B29" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>138</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
